--- a/research/traditional_assets/database/data/uganda/uganda_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/uganda/uganda_insurance_general.xlsx
@@ -639,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.08288873247043339</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AB2">
-        <v>0.08288873247043339</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.08288873247043339</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AB3">
-        <v>0.08288873247043339</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AD3">
         <v>0</v>

--- a/research/traditional_assets/database/data/uganda/uganda_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/uganda/uganda_insurance_general.xlsx
@@ -588,50 +588,53 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.168</v>
+        <v>0.142</v>
       </c>
       <c r="E2">
-        <v>-0.00121</v>
+        <v>0.0438</v>
       </c>
       <c r="G2">
-        <v>0.022</v>
+        <v>0.1255605381165919</v>
       </c>
       <c r="H2">
-        <v>0.022</v>
+        <v>0.1255605381165919</v>
       </c>
       <c r="I2">
-        <v>0.002</v>
+        <v>0.1106128550074738</v>
       </c>
       <c r="J2">
-        <v>0.001409703504043127</v>
+        <v>0.1106128550074738</v>
       </c>
       <c r="K2">
-        <v>0.523</v>
+        <v>1.14</v>
       </c>
       <c r="L2">
-        <v>0.1162222222222222</v>
+        <v>0.1704035874439462</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0002747252747252747</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.0008771929824561405</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.0002747252747252747</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0008771929824561405</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
         <v>0</v>
       </c>
@@ -639,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1330936372347507</v>
+        <v>0.1175091231509749</v>
       </c>
       <c r="AB2">
-        <v>0.1330936372347507</v>
+        <v>0.1175091231509749</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -663,22 +666,22 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>0.243</v>
+        <v>0.28</v>
       </c>
       <c r="AM2">
-        <v>0.243</v>
+        <v>0.28</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>0.03703703703703703</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.03703703703703703</v>
+        <v>2.642857142857143</v>
       </c>
     </row>
     <row r="3">
@@ -698,50 +701,53 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.168</v>
+        <v>0.142</v>
       </c>
       <c r="E3">
-        <v>-0.00121</v>
+        <v>0.0438</v>
       </c>
       <c r="G3">
-        <v>0.022</v>
+        <v>0.1255605381165919</v>
       </c>
       <c r="H3">
-        <v>0.022</v>
+        <v>0.1255605381165919</v>
       </c>
       <c r="I3">
-        <v>0.002</v>
+        <v>0.1106128550074738</v>
       </c>
       <c r="J3">
-        <v>0.001409703504043127</v>
+        <v>0.1106128550074738</v>
       </c>
       <c r="K3">
-        <v>0.523</v>
+        <v>1.14</v>
       </c>
       <c r="L3">
-        <v>0.1162222222222222</v>
+        <v>0.1704035874439462</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0002747252747252747</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.0008771929824561405</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0002747252747252747</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.0008771929824561405</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
         <v>0</v>
       </c>
@@ -749,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1330936372347507</v>
+        <v>0.1175091231509749</v>
       </c>
       <c r="AB3">
-        <v>0.1330936372347507</v>
+        <v>0.1175091231509749</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -773,22 +779,22 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>0.243</v>
+        <v>0.28</v>
       </c>
       <c r="AM3">
-        <v>0.243</v>
+        <v>0.28</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>0.03703703703703703</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.03703703703703703</v>
+        <v>2.642857142857143</v>
       </c>
     </row>
   </sheetData>
